--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.96111451932067</v>
+        <v>7.95618110938961</v>
       </c>
       <c r="D2" t="n">
-        <v>47.09914971608355</v>
+        <v>7.653611828863577</v>
       </c>
       <c r="E2" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F2" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.29927354242476</v>
+        <v>5.573631950644023</v>
       </c>
       <c r="D3" t="n">
-        <v>34.69547933004142</v>
+        <v>5.63801539113173</v>
       </c>
       <c r="E3" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F3" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.838164427979</v>
+        <v>6.798701719546587</v>
       </c>
       <c r="D4" t="n">
-        <v>41.51626778194461</v>
+        <v>6.746393514565999</v>
       </c>
       <c r="E4" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F4" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.72886093909343</v>
+        <v>3.855939902602683</v>
       </c>
       <c r="D5" t="n">
-        <v>15.88955795880429</v>
+        <v>2.582053168305697</v>
       </c>
       <c r="E5" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F5" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.16700425202681</v>
+        <v>7.664638190954356</v>
       </c>
       <c r="D6" t="n">
-        <v>37.18965776555078</v>
+        <v>6.043319386902002</v>
       </c>
       <c r="E6" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F6" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.09743964331692</v>
+        <v>7.003333942038999</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09413665580919</v>
+        <v>5.215297206568994</v>
       </c>
       <c r="E7" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F7" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.95920750265672</v>
+        <v>2.593371219181716</v>
       </c>
       <c r="D8" t="n">
-        <v>16.55637603309924</v>
+        <v>2.690411105378626</v>
       </c>
       <c r="E8" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F8" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61352043247091</v>
+        <v>5.462197070276524</v>
       </c>
       <c r="D9" t="n">
-        <v>22.14673908561257</v>
+        <v>3.598845101412043</v>
       </c>
       <c r="E9" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F9" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.14816504762671</v>
+        <v>4.411576820239341</v>
       </c>
       <c r="D10" t="n">
-        <v>27.12057985778123</v>
+        <v>4.40709422688945</v>
       </c>
       <c r="E10" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F10" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.81889882593642</v>
+        <v>6.633071059214668</v>
       </c>
       <c r="D11" t="n">
-        <v>40.20105409076617</v>
+        <v>6.532671289749503</v>
       </c>
       <c r="E11" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F11" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.52557536638924</v>
+        <v>3.497905997038252</v>
       </c>
       <c r="D12" t="n">
-        <v>20.10245533405599</v>
+        <v>3.266648991784098</v>
       </c>
       <c r="E12" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F12" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.56359007943703</v>
+        <v>6.429083387908518</v>
       </c>
       <c r="D13" t="n">
-        <v>41.95497013441761</v>
+        <v>6.817682646842862</v>
       </c>
       <c r="E13" t="n">
-        <v>10.18473493845386</v>
+        <v>1.655019427498752</v>
       </c>
       <c r="F13" t="n">
-        <v>10.30777820435608</v>
+        <v>1.675013958207863</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
